--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/148.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/148.xlsx
@@ -426,13 +426,13 @@
         <v>-12.73975917059843</v>
       </c>
       <c r="E2">
-        <v>-17.75809137613236</v>
+        <v>-17.33724217270353</v>
       </c>
       <c r="F2">
-        <v>-6.372746548420497</v>
+        <v>-6.334896785051781</v>
       </c>
       <c r="G2">
-        <v>-15.42148920935778</v>
+        <v>-14.68842493831912</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.8351603737466</v>
       </c>
       <c r="E3">
-        <v>-18.31557369732063</v>
+        <v>-19.65250602165714</v>
       </c>
       <c r="F3">
-        <v>-6.321802781515729</v>
+        <v>-6.34878602129452</v>
       </c>
       <c r="G3">
-        <v>-15.09568031461272</v>
+        <v>-14.44763577540083</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.88987451634554</v>
       </c>
       <c r="E4">
-        <v>-18.5542469198949</v>
+        <v>-20.58690681992583</v>
       </c>
       <c r="F4">
-        <v>-6.046719362761473</v>
+        <v>-5.750225131747056</v>
       </c>
       <c r="G4">
-        <v>-15.55332212917315</v>
+        <v>-13.77820095284292</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.88508403967594</v>
       </c>
       <c r="E5">
-        <v>-18.51303327795109</v>
+        <v>-20.54920727381197</v>
       </c>
       <c r="F5">
-        <v>-6.271742054262347</v>
+        <v>-6.412914083782244</v>
       </c>
       <c r="G5">
-        <v>-15.58536325770113</v>
+        <v>-13.83373234651496</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.79680183460744</v>
       </c>
       <c r="E6">
-        <v>-19.7926441782985</v>
+        <v>-20.82854619297512</v>
       </c>
       <c r="F6">
-        <v>-6.073620594167386</v>
+        <v>-6.265895437133388</v>
       </c>
       <c r="G6">
-        <v>-15.76735785210651</v>
+        <v>-13.83836215013534</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.61629975081954</v>
       </c>
       <c r="E7">
-        <v>-20.2077422197376</v>
+        <v>-20.8134210897895</v>
       </c>
       <c r="F7">
-        <v>-5.812991358224578</v>
+        <v>-6.895125801402101</v>
       </c>
       <c r="G7">
-        <v>-15.33995413482714</v>
+        <v>-13.23269294675289</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.33820285399026</v>
       </c>
       <c r="E8">
-        <v>-20.65898654070592</v>
+        <v>-20.9978567791739</v>
       </c>
       <c r="F8">
-        <v>-6.062116227677307</v>
+        <v>-5.949678606625719</v>
       </c>
       <c r="G8">
-        <v>-14.72820810911661</v>
+        <v>-13.91721154481957</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.95684487925932</v>
       </c>
       <c r="E9">
-        <v>-21.3631868912687</v>
+        <v>-22.50273661903287</v>
       </c>
       <c r="F9">
-        <v>-6.235460804570833</v>
+        <v>-5.955201332100184</v>
       </c>
       <c r="G9">
-        <v>-14.86997984903553</v>
+        <v>-13.02667160747848</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.48451525074432</v>
       </c>
       <c r="E10">
-        <v>-21.6410223570613</v>
+        <v>-23.49392900983176</v>
       </c>
       <c r="F10">
-        <v>-5.888772064967482</v>
+        <v>-5.796751215292693</v>
       </c>
       <c r="G10">
-        <v>-14.58601473222729</v>
+        <v>-13.34824772641186</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.92172584437036</v>
       </c>
       <c r="E11">
-        <v>-22.4322011078894</v>
+        <v>-21.9149633352073</v>
       </c>
       <c r="F11">
-        <v>-6.455425070526513</v>
+        <v>-5.76824626459496</v>
       </c>
       <c r="G11">
-        <v>-14.02748683898939</v>
+        <v>-12.95063914150303</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.30566132635498</v>
       </c>
       <c r="E12">
-        <v>-23.59753143817924</v>
+        <v>-24.68047976932155</v>
       </c>
       <c r="F12">
-        <v>-6.156217107900525</v>
+        <v>-5.816718183169773</v>
       </c>
       <c r="G12">
-        <v>-13.91522640577611</v>
+        <v>-12.09759372292171</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.657057626719173</v>
       </c>
       <c r="E13">
-        <v>-23.36369915431918</v>
+        <v>-24.69321383823112</v>
       </c>
       <c r="F13">
-        <v>-6.211886710838264</v>
+        <v>-6.104377875833332</v>
       </c>
       <c r="G13">
-        <v>-13.41402309379249</v>
+        <v>-11.92549365212883</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.035872319754539</v>
       </c>
       <c r="E14">
-        <v>-24.90040510950406</v>
+        <v>-25.25463140333205</v>
       </c>
       <c r="F14">
-        <v>-5.791390849829178</v>
+        <v>-5.639605777144613</v>
       </c>
       <c r="G14">
-        <v>-13.59165858535615</v>
+        <v>-10.34911606565417</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.481796143026118</v>
       </c>
       <c r="E15">
-        <v>-25.33805042302735</v>
+        <v>-27.57267573532637</v>
       </c>
       <c r="F15">
-        <v>-6.003756915782679</v>
+        <v>-5.672505216914199</v>
       </c>
       <c r="G15">
-        <v>-12.75815940360444</v>
+        <v>-11.30873884170781</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.043102407371716</v>
       </c>
       <c r="E16">
-        <v>-24.87930694910232</v>
+        <v>-26.71421744616631</v>
       </c>
       <c r="F16">
-        <v>-5.64541594610785</v>
+        <v>-5.652416479028908</v>
       </c>
       <c r="G16">
-        <v>-12.73029198890008</v>
+        <v>-10.51893240624167</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.746333714182427</v>
       </c>
       <c r="E17">
-        <v>-25.41195059035852</v>
+        <v>-28.68319794470138</v>
       </c>
       <c r="F17">
-        <v>-5.650724124424989</v>
+        <v>-4.595847110636583</v>
       </c>
       <c r="G17">
-        <v>-11.66082703992246</v>
+        <v>-10.92549544478622</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.598322139069937</v>
       </c>
       <c r="E18">
-        <v>-27.15669916992978</v>
+        <v>-26.83102490472016</v>
       </c>
       <c r="F18">
-        <v>-5.508316170740114</v>
+        <v>-4.937642269807895</v>
       </c>
       <c r="G18">
-        <v>-11.67126460570306</v>
+        <v>-10.56923353274795</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.597634837970613</v>
       </c>
       <c r="E19">
-        <v>-27.68226027783798</v>
+        <v>-28.19497410498642</v>
       </c>
       <c r="F19">
-        <v>-5.179006993431199</v>
+        <v>-4.83317685664085</v>
       </c>
       <c r="G19">
-        <v>-12.12503457882334</v>
+        <v>-11.75298999108415</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.708811690147827</v>
       </c>
       <c r="E20">
-        <v>-28.75226170179236</v>
+        <v>-28.19563526219154</v>
       </c>
       <c r="F20">
-        <v>-5.21412148763587</v>
+        <v>-4.429514249624054</v>
       </c>
       <c r="G20">
-        <v>-10.97699093594015</v>
+        <v>-11.07616585757436</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.910346344744725</v>
       </c>
       <c r="E21">
-        <v>-28.16515410364591</v>
+        <v>-29.00200251484137</v>
       </c>
       <c r="F21">
-        <v>-4.670430826482442</v>
+        <v>-4.266909041924122</v>
       </c>
       <c r="G21">
-        <v>-11.40147600664239</v>
+        <v>-10.55889440361414</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.149525633059262</v>
       </c>
       <c r="E22">
-        <v>-30.25195870314955</v>
+        <v>-30.34938429295057</v>
       </c>
       <c r="F22">
-        <v>-4.767361409753624</v>
+        <v>-4.407728186930426</v>
       </c>
       <c r="G22">
-        <v>-12.16143973202538</v>
+        <v>-10.67605698183724</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.39921944215048</v>
       </c>
       <c r="E23">
-        <v>-29.93303865692237</v>
+        <v>-30.09696488752602</v>
       </c>
       <c r="F23">
-        <v>-4.714020347585155</v>
+        <v>-3.569817163283268</v>
       </c>
       <c r="G23">
-        <v>-11.07016450334214</v>
+        <v>-10.81577795828151</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.615025678077055</v>
       </c>
       <c r="E24">
-        <v>-30.20647471021651</v>
+        <v>-31.13552285220814</v>
       </c>
       <c r="F24">
-        <v>-4.539676345420151</v>
+        <v>-4.01302520174231</v>
       </c>
       <c r="G24">
-        <v>-12.02246031165354</v>
+        <v>-10.08021995885767</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.773283299011151</v>
       </c>
       <c r="E25">
-        <v>-30.95671152754127</v>
+        <v>-32.5724982243221</v>
       </c>
       <c r="F25">
-        <v>-4.527224326621269</v>
+        <v>-3.360174769350172</v>
       </c>
       <c r="G25">
-        <v>-11.4087570372828</v>
+        <v>-10.43918887868248</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.851447594198442</v>
       </c>
       <c r="E26">
-        <v>-30.32183984979892</v>
+        <v>-32.13958290189982</v>
       </c>
       <c r="F26">
-        <v>-4.631722046117024</v>
+        <v>-3.910571064629262</v>
       </c>
       <c r="G26">
-        <v>-11.64670794355217</v>
+        <v>-10.43982543566501</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.836879598660097</v>
       </c>
       <c r="E27">
-        <v>-30.62353131666393</v>
+        <v>-31.28555119608226</v>
       </c>
       <c r="F27">
-        <v>-4.270165354184527</v>
+        <v>-3.730956989047647</v>
       </c>
       <c r="G27">
-        <v>-10.947148225857</v>
+        <v>-11.31503550588038</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.732284158243159</v>
       </c>
       <c r="E28">
-        <v>-30.92905160830242</v>
+        <v>-32.354585790836</v>
       </c>
       <c r="F28">
-        <v>-3.953532683240652</v>
+        <v>-3.545960182082642</v>
       </c>
       <c r="G28">
-        <v>-11.24137208187085</v>
+        <v>-10.37866018457541</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.536292927832172</v>
       </c>
       <c r="E29">
-        <v>-30.39748347962304</v>
+        <v>-30.07603654489958</v>
       </c>
       <c r="F29">
-        <v>-4.535627285555267</v>
+        <v>-3.786927289352602</v>
       </c>
       <c r="G29">
-        <v>-11.80720889613241</v>
+        <v>-10.81421281559766</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.269101417383068</v>
       </c>
       <c r="E30">
-        <v>-29.41206942165794</v>
+        <v>-31.59524674075582</v>
       </c>
       <c r="F30">
-        <v>-4.192948258365168</v>
+        <v>-3.541668410568738</v>
       </c>
       <c r="G30">
-        <v>-11.45379180318618</v>
+        <v>-10.5745130182371</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.936803869789271</v>
       </c>
       <c r="E31">
-        <v>-30.29374066858133</v>
+        <v>-30.24792383280872</v>
       </c>
       <c r="F31">
-        <v>-4.378625154967872</v>
+        <v>-3.661223364345179</v>
       </c>
       <c r="G31">
-        <v>-11.62208893819166</v>
+        <v>-10.53043965025064</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.566940850032082</v>
       </c>
       <c r="E32">
-        <v>-29.50138451451123</v>
+        <v>-31.98203729117297</v>
       </c>
       <c r="F32">
-        <v>-4.369098929835677</v>
+        <v>-3.171321912125135</v>
       </c>
       <c r="G32">
-        <v>-11.27287180884152</v>
+        <v>-10.20556590365002</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.17349255033363</v>
       </c>
       <c r="E33">
-        <v>-30.15140167357223</v>
+        <v>-30.45741330464055</v>
       </c>
       <c r="F33">
-        <v>-4.758042276472129</v>
+        <v>-3.4600485420035</v>
       </c>
       <c r="G33">
-        <v>-11.16812865422092</v>
+        <v>-11.87004428899578</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.782859801932371</v>
       </c>
       <c r="E34">
-        <v>-29.22082290736601</v>
+        <v>-30.64872095333159</v>
       </c>
       <c r="F34">
-        <v>-4.422610635689122</v>
+        <v>-3.497865170676103</v>
       </c>
       <c r="G34">
-        <v>-11.25366025661097</v>
+        <v>-10.10269960776143</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.415363282336005</v>
       </c>
       <c r="E35">
-        <v>-30.02600596406283</v>
+        <v>-29.68714704677987</v>
       </c>
       <c r="F35">
-        <v>-4.067873892583874</v>
+        <v>-3.982995226656022</v>
       </c>
       <c r="G35">
-        <v>-10.4258375881571</v>
+        <v>-10.23432252939699</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.089788516796102</v>
       </c>
       <c r="E36">
-        <v>-28.91775478440267</v>
+        <v>-30.14225415607673</v>
       </c>
       <c r="F36">
-        <v>-4.449698249760666</v>
+        <v>-3.758427308859285</v>
       </c>
       <c r="G36">
-        <v>-10.58915382883534</v>
+        <v>-10.59979811157418</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.826716025224104</v>
       </c>
       <c r="E37">
-        <v>-28.78960349845961</v>
+        <v>-30.84332985957422</v>
       </c>
       <c r="F37">
-        <v>-4.768859926385288</v>
+        <v>-3.628867333591831</v>
       </c>
       <c r="G37">
-        <v>-10.78006514282852</v>
+        <v>-9.429379818877132</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.628565578760389</v>
       </c>
       <c r="E38">
-        <v>-28.34569077690971</v>
+        <v>-30.01933778608654</v>
       </c>
       <c r="F38">
-        <v>-4.358655701988584</v>
+        <v>-3.787610692459911</v>
       </c>
       <c r="G38">
-        <v>-11.13072929088637</v>
+        <v>-9.801007691478281</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.509746844209227</v>
       </c>
       <c r="E39">
-        <v>-27.43610148772904</v>
+        <v>-28.4323567124685</v>
       </c>
       <c r="F39">
-        <v>-4.378397353932102</v>
+        <v>-3.875632184313984</v>
       </c>
       <c r="G39">
-        <v>-11.01671340413879</v>
+        <v>-9.092099773560252</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.45849698481967</v>
       </c>
       <c r="E40">
-        <v>-27.74075457659506</v>
+        <v>-29.7073553620391</v>
       </c>
       <c r="F40">
-        <v>-4.329925435357289</v>
+        <v>-3.661690563560358</v>
       </c>
       <c r="G40">
-        <v>-10.90318970062512</v>
+        <v>-10.08803582861227</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.479667496464245</v>
       </c>
       <c r="E41">
-        <v>-27.78788240559289</v>
+        <v>-28.21644360025678</v>
       </c>
       <c r="F41">
-        <v>-4.314905477609728</v>
+        <v>-3.820097605262902</v>
       </c>
       <c r="G41">
-        <v>-10.47603699679505</v>
+        <v>-9.164936329736804</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.557068954757495</v>
       </c>
       <c r="E42">
-        <v>-26.97471791345754</v>
+        <v>-28.59711165381556</v>
       </c>
       <c r="F42">
-        <v>-4.551229585586996</v>
+        <v>-3.73689638332572</v>
       </c>
       <c r="G42">
-        <v>-10.57342365267936</v>
+        <v>-9.514698141865814</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.686412338492529</v>
       </c>
       <c r="E43">
-        <v>-25.82031479094821</v>
+        <v>-27.46961672385981</v>
       </c>
       <c r="F43">
-        <v>-4.516089411992838</v>
+        <v>-3.600819641700442</v>
       </c>
       <c r="G43">
-        <v>-10.32098943444661</v>
+        <v>-10.58909148562571</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.852634778812202</v>
       </c>
       <c r="E44">
-        <v>-26.62142448527513</v>
+        <v>-27.60295764101566</v>
       </c>
       <c r="F44">
-        <v>-4.501694043266989</v>
+        <v>-3.888279697819927</v>
       </c>
       <c r="G44">
-        <v>-10.98111871266193</v>
+        <v>-9.296247535324223</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.04261405060507</v>
       </c>
       <c r="E45">
-        <v>-25.75518627776989</v>
+        <v>-26.51765450338937</v>
       </c>
       <c r="F45">
-        <v>-4.591310142371451</v>
+        <v>-3.915488253532279</v>
       </c>
       <c r="G45">
-        <v>-11.00352289346982</v>
+        <v>-9.85550221913754</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.248951078769822</v>
       </c>
       <c r="E46">
-        <v>-25.95992764460469</v>
+        <v>-25.5679202921307</v>
       </c>
       <c r="F46">
-        <v>-4.552484562202237</v>
+        <v>-3.312448381437878</v>
       </c>
       <c r="G46">
-        <v>-10.76807227802875</v>
+        <v>-8.990234250247291</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.454942722685587</v>
       </c>
       <c r="E47">
-        <v>-26.25881145758494</v>
+        <v>-25.48731798326818</v>
       </c>
       <c r="F47">
-        <v>-4.530105388448206</v>
+        <v>-4.314540995952497</v>
       </c>
       <c r="G47">
-        <v>-10.89246010612573</v>
+        <v>-11.1963832530693</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.662011816003231</v>
       </c>
       <c r="E48">
-        <v>-24.76136737204656</v>
+        <v>-26.69860779626187</v>
       </c>
       <c r="F48">
-        <v>-4.735729372110322</v>
+        <v>-3.983923826514561</v>
       </c>
       <c r="G48">
-        <v>-11.57376638828572</v>
+        <v>-10.11054828973162</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.85595421141383</v>
       </c>
       <c r="E49">
-        <v>-24.48743545084857</v>
+        <v>-24.82736535223435</v>
       </c>
       <c r="F49">
-        <v>-4.783025008973159</v>
+        <v>-4.264684875447605</v>
       </c>
       <c r="G49">
-        <v>-10.95622080346886</v>
+        <v>-9.618611147431869</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.045110555234171</v>
       </c>
       <c r="E50">
-        <v>-23.59471472734647</v>
+        <v>-24.59806154238195</v>
       </c>
       <c r="F50">
-        <v>-4.329888987191565</v>
+        <v>-4.151707158849392</v>
       </c>
       <c r="G50">
-        <v>-11.42490392857683</v>
+        <v>-10.72626623413986</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.222983048653295</v>
       </c>
       <c r="E51">
-        <v>-24.23516774930328</v>
+        <v>-24.99428490415707</v>
       </c>
       <c r="F51">
-        <v>-4.369166855962707</v>
+        <v>-4.53144403017113</v>
       </c>
       <c r="G51">
-        <v>-11.0544638581802</v>
+        <v>-10.75716221634359</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.398708355800229</v>
       </c>
       <c r="E52">
-        <v>-23.31881291995515</v>
+        <v>-25.34248379908086</v>
       </c>
       <c r="F52">
-        <v>-4.785516738120781</v>
+        <v>-4.41521248641472</v>
       </c>
       <c r="G52">
-        <v>-11.31748657838529</v>
+        <v>-9.901357290430779</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.573986713004207</v>
       </c>
       <c r="E53">
-        <v>-21.69790904754565</v>
+        <v>-23.42968354908494</v>
       </c>
       <c r="F53">
-        <v>-4.625937556543275</v>
+        <v>-4.347178671622797</v>
       </c>
       <c r="G53">
-        <v>-11.47045384626504</v>
+        <v>-8.723982808027708</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.753224207051256</v>
       </c>
       <c r="E54">
-        <v>-22.57925877281449</v>
+        <v>-22.81562700211885</v>
       </c>
       <c r="F54">
-        <v>-4.699640717839959</v>
+        <v>-4.662276377769284</v>
       </c>
       <c r="G54">
-        <v>-11.3989429035985</v>
+        <v>-9.833258818186064</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.943277756851033</v>
       </c>
       <c r="E55">
-        <v>-21.70535838728827</v>
+        <v>-24.56134467512776</v>
       </c>
       <c r="F55">
-        <v>-4.689983610658122</v>
+        <v>-4.304912881629757</v>
       </c>
       <c r="G55">
-        <v>-11.62081910544815</v>
+        <v>-9.72260290231535</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.140364880831436</v>
       </c>
       <c r="E56">
-        <v>-21.47489981656392</v>
+        <v>-21.81960272955378</v>
       </c>
       <c r="F56">
-        <v>-4.792028534274188</v>
+        <v>-4.412190602129308</v>
       </c>
       <c r="G56">
-        <v>-10.86381176069022</v>
+        <v>-9.332157224070786</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.354241577670734</v>
       </c>
       <c r="E57">
-        <v>-21.14547144640193</v>
+        <v>-23.09230770703949</v>
       </c>
       <c r="F57">
-        <v>-4.449151527274819</v>
+        <v>-4.030454051897212</v>
       </c>
       <c r="G57">
-        <v>-11.61932614963861</v>
+        <v>-10.17510632391369</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.572568704781482</v>
       </c>
       <c r="E58">
-        <v>-21.11009500745401</v>
+        <v>-21.44595381070689</v>
       </c>
       <c r="F58">
-        <v>-4.537063674631722</v>
+        <v>-4.302376420642386</v>
       </c>
       <c r="G58">
-        <v>-11.82386765798971</v>
+        <v>-10.43122863517927</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.803410850379956</v>
       </c>
       <c r="E59">
-        <v>-22.11054812759858</v>
+        <v>-22.13617476200799</v>
       </c>
       <c r="F59">
-        <v>-4.428848242232203</v>
+        <v>-4.019951181597117</v>
       </c>
       <c r="G59">
-        <v>-12.22257873334252</v>
+        <v>-10.42069591397345</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.031763760925431</v>
       </c>
       <c r="E60">
-        <v>-21.19975426433187</v>
+        <v>-22.04077792856241</v>
       </c>
       <c r="F60">
-        <v>-4.541589874120619</v>
+        <v>-3.781382197958262</v>
       </c>
       <c r="G60">
-        <v>-12.07882841682324</v>
+        <v>-11.00615115193893</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.258815779737416</v>
       </c>
       <c r="E61">
-        <v>-20.72050133162611</v>
+        <v>-21.39869465596284</v>
       </c>
       <c r="F61">
-        <v>-4.446694589558115</v>
+        <v>-4.356395915713747</v>
       </c>
       <c r="G61">
-        <v>-12.67277873740613</v>
+        <v>-10.44414024201568</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.475459585354246</v>
       </c>
       <c r="E62">
-        <v>-19.85934407195748</v>
+        <v>-21.14114675372461</v>
       </c>
       <c r="F62">
-        <v>-4.516384310788235</v>
+        <v>-4.191086916811078</v>
       </c>
       <c r="G62">
-        <v>-12.98085262962239</v>
+        <v>-10.87539447279506</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.677585987701924</v>
       </c>
       <c r="E63">
-        <v>-20.0276719792966</v>
+        <v>-20.45511011240659</v>
       </c>
       <c r="F63">
-        <v>-4.473849301389286</v>
+        <v>-4.256425224074292</v>
       </c>
       <c r="G63">
-        <v>-13.03334233090883</v>
+        <v>-10.34370205008108</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.863966368890669</v>
       </c>
       <c r="E64">
-        <v>-19.4574782315688</v>
+        <v>-20.40951290762336</v>
       </c>
       <c r="F64">
-        <v>-4.215060697815498</v>
+        <v>-3.568864540770049</v>
       </c>
       <c r="G64">
-        <v>-13.21955821685044</v>
+        <v>-10.98334009965767</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.02648079518513</v>
       </c>
       <c r="E65">
-        <v>-20.26864113819275</v>
+        <v>-20.84045155114129</v>
       </c>
       <c r="F65">
-        <v>-4.276636560335197</v>
+        <v>-4.403160569071391</v>
       </c>
       <c r="G65">
-        <v>-13.05913601358763</v>
+        <v>-11.02853236419591</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.17369973503503</v>
       </c>
       <c r="E66">
-        <v>-19.24104887332021</v>
+        <v>-21.12089994643631</v>
       </c>
       <c r="F66">
-        <v>-4.637826285508254</v>
+        <v>-4.541869033935362</v>
       </c>
       <c r="G66">
-        <v>-13.05004046742484</v>
+        <v>-11.74313648274113</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.29327495293825</v>
       </c>
       <c r="E67">
-        <v>-20.00613455691611</v>
+        <v>-21.35442882253786</v>
       </c>
       <c r="F67">
-        <v>-4.525820243873524</v>
+        <v>-4.217361074093072</v>
       </c>
       <c r="G67">
-        <v>-13.30019423667379</v>
+        <v>-13.13762939573266</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.39991514689234</v>
       </c>
       <c r="E68">
-        <v>-19.73919007111196</v>
+        <v>-20.64130737817997</v>
       </c>
       <c r="F68">
-        <v>-4.497315293175791</v>
+        <v>-4.523002966336603</v>
       </c>
       <c r="G68">
-        <v>-13.32200123515786</v>
+        <v>-11.60558111252609</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.48444950390974</v>
       </c>
       <c r="E69">
-        <v>-19.83301552407688</v>
+        <v>-19.00257943207628</v>
       </c>
       <c r="F69">
-        <v>-4.593692527021902</v>
+        <v>-4.236126080868689</v>
       </c>
       <c r="G69">
-        <v>-13.53696390318176</v>
+        <v>-12.21734190373364</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.55824772008962</v>
       </c>
       <c r="E70">
-        <v>-19.19336404201944</v>
+        <v>-20.38548482453866</v>
       </c>
       <c r="F70">
-        <v>-4.403095956413972</v>
+        <v>-5.089662598834855</v>
       </c>
       <c r="G70">
-        <v>-12.81303455296459</v>
+        <v>-11.77917413912851</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.61869100912895</v>
       </c>
       <c r="E71">
-        <v>-20.08002566729927</v>
+        <v>-18.83374886412232</v>
       </c>
       <c r="F71">
-        <v>-4.651847232168039</v>
+        <v>-4.455920117323093</v>
       </c>
       <c r="G71">
-        <v>-13.55089925114472</v>
+        <v>-11.97847553664919</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.66876045385419</v>
       </c>
       <c r="E72">
-        <v>-20.45554031743732</v>
+        <v>-19.34974583492632</v>
       </c>
       <c r="F72">
-        <v>-4.6774901734891</v>
+        <v>-4.57965749811627</v>
       </c>
       <c r="G72">
-        <v>-13.11673129562056</v>
+        <v>-12.26868645869583</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.71134400040703</v>
       </c>
       <c r="E73">
-        <v>-20.38366437798758</v>
+        <v>-20.38044916144213</v>
       </c>
       <c r="F73">
-        <v>-4.47518794311221</v>
+        <v>-4.259361786517216</v>
       </c>
       <c r="G73">
-        <v>-13.0311767246796</v>
+        <v>-11.58827266880002</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.73917438064831</v>
       </c>
       <c r="E74">
-        <v>-20.16829015418277</v>
+        <v>-19.79475444718608</v>
       </c>
       <c r="F74">
-        <v>-4.408858080067845</v>
+        <v>-4.484430866592647</v>
       </c>
       <c r="G74">
-        <v>-13.23118358483555</v>
+        <v>-11.92784300676539</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.76049066170115</v>
       </c>
       <c r="E75">
-        <v>-20.51578713563537</v>
+        <v>-19.3355083126462</v>
       </c>
       <c r="F75">
-        <v>-4.82601313534144</v>
+        <v>-4.786384867158914</v>
       </c>
       <c r="G75">
-        <v>-13.25849319187481</v>
+        <v>-11.58678627543359</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.76037561229252</v>
       </c>
       <c r="E76">
-        <v>-20.3824416900055</v>
+        <v>-19.85041844968836</v>
       </c>
       <c r="F76">
-        <v>-4.872559928072147</v>
+        <v>-5.42666482421357</v>
       </c>
       <c r="G76">
-        <v>-12.16505891940545</v>
+        <v>-11.15425893068915</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.75016608658072</v>
       </c>
       <c r="E77">
-        <v>-20.52264324528298</v>
+        <v>-21.90678943962346</v>
       </c>
       <c r="F77">
-        <v>-4.659676960859299</v>
+        <v>-4.581054953924792</v>
       </c>
       <c r="G77">
-        <v>-12.49974351846881</v>
+        <v>-10.47308389739154</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.71487408254188</v>
       </c>
       <c r="E78">
-        <v>-20.76056926964598</v>
+        <v>-21.00868888900025</v>
       </c>
       <c r="F78">
-        <v>-4.818668001580817</v>
+        <v>-4.92246989245822</v>
       </c>
       <c r="G78">
-        <v>-12.67907212035714</v>
+        <v>-10.96193997264698</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.66233580060955</v>
       </c>
       <c r="E79">
-        <v>-20.72028396487374</v>
+        <v>-22.26302637591085</v>
       </c>
       <c r="F79">
-        <v>-4.843422104678674</v>
+        <v>-4.985863193059661</v>
       </c>
       <c r="G79">
-        <v>-12.36726091678467</v>
+        <v>-10.64308726760794</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.58578090704463</v>
       </c>
       <c r="E80">
-        <v>-21.9411152726016</v>
+        <v>-22.57694925107058</v>
       </c>
       <c r="F80">
-        <v>-5.192709847008309</v>
+        <v>-5.1956662902689</v>
       </c>
       <c r="G80">
-        <v>-12.12474583132611</v>
+        <v>-10.69436619813894</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.48775950848767</v>
       </c>
       <c r="E81">
-        <v>-22.96378961470181</v>
+        <v>-21.80242622764268</v>
       </c>
       <c r="F81">
-        <v>-4.794409262189833</v>
+        <v>-6.127194427576041</v>
       </c>
       <c r="G81">
-        <v>-11.85745096065063</v>
+        <v>-11.12282810937123</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.3718581091142</v>
       </c>
       <c r="E82">
-        <v>-23.11963704767578</v>
+        <v>-22.24734427042229</v>
       </c>
       <c r="F82">
-        <v>-4.885791440597063</v>
+        <v>-5.426462702567287</v>
       </c>
       <c r="G82">
-        <v>-12.35898895723331</v>
+        <v>-10.56892181669981</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.23498872553784</v>
       </c>
       <c r="E83">
-        <v>-22.99048044050302</v>
+        <v>-24.47580632959687</v>
       </c>
       <c r="F83">
-        <v>-5.312862053682168</v>
+        <v>-5.002393264582524</v>
       </c>
       <c r="G83">
-        <v>-11.67406348769326</v>
+        <v>-10.76770149999253</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.09103167264221</v>
       </c>
       <c r="E84">
-        <v>-24.17803652122251</v>
+        <v>-23.71538044575486</v>
       </c>
       <c r="F84">
-        <v>-5.239383379951644</v>
+        <v>-5.028321992657552</v>
       </c>
       <c r="G84">
-        <v>-11.5530389116947</v>
+        <v>-9.939311180208877</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.933106185669384</v>
       </c>
       <c r="E85">
-        <v>-25.52089661803505</v>
+        <v>-25.64772106109387</v>
       </c>
       <c r="F85">
-        <v>-5.527762923888235</v>
+        <v>-5.603081401620377</v>
       </c>
       <c r="G85">
-        <v>-11.82257485669529</v>
+        <v>-8.463037101069748</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.784817913907663</v>
       </c>
       <c r="E86">
-        <v>-25.84422513370871</v>
+        <v>-27.26900985379402</v>
       </c>
       <c r="F86">
-        <v>-5.631806698047257</v>
+        <v>-5.303374761817905</v>
       </c>
       <c r="G86">
-        <v>-11.64339390977713</v>
+        <v>-10.41693891528789</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.643840958730101</v>
       </c>
       <c r="E87">
-        <v>-27.56564754366646</v>
+        <v>-28.25892521492274</v>
       </c>
       <c r="F87">
-        <v>-5.562962739935394</v>
+        <v>-4.887178955996752</v>
       </c>
       <c r="G87">
-        <v>-11.83144071734891</v>
+        <v>-10.26677052939834</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.534694085290189</v>
       </c>
       <c r="E88">
-        <v>-28.29023961268578</v>
+        <v>-28.93562414283694</v>
       </c>
       <c r="F88">
-        <v>-5.478971255495942</v>
+        <v>-5.238001663123774</v>
       </c>
       <c r="G88">
-        <v>-11.28059908561401</v>
+        <v>-10.74257718651186</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.463801382756884</v>
       </c>
       <c r="E89">
-        <v>-30.64151162271138</v>
+        <v>-29.87704181158052</v>
       </c>
       <c r="F89">
-        <v>-5.808027780747003</v>
+        <v>-5.681765536110094</v>
       </c>
       <c r="G89">
-        <v>-11.59804742782561</v>
+        <v>-11.08352235631064</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.447059956038052</v>
       </c>
       <c r="E90">
-        <v>-30.85082901253092</v>
+        <v>-31.09278085028674</v>
       </c>
       <c r="F90">
-        <v>-5.853833184652204</v>
+        <v>-6.11308236050195</v>
       </c>
       <c r="G90">
-        <v>-11.75892900210674</v>
+        <v>-10.04462854860237</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.495899521404947</v>
       </c>
       <c r="E91">
-        <v>-32.20688055412781</v>
+        <v>-32.85644939426206</v>
       </c>
       <c r="F91">
-        <v>-5.57688014066983</v>
+        <v>-6.136236057777598</v>
       </c>
       <c r="G91">
-        <v>-11.64151048860201</v>
+        <v>-10.22322543808295</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.611090759255612</v>
       </c>
       <c r="E92">
-        <v>-34.49805744983463</v>
+        <v>-35.1497116522494</v>
       </c>
       <c r="F92">
-        <v>-5.916808159715232</v>
+        <v>-5.60230107952694</v>
       </c>
       <c r="G92">
-        <v>-12.18262329841316</v>
+        <v>-11.17880574917536</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.806696103940245</v>
       </c>
       <c r="E93">
-        <v>-35.73503956011083</v>
+        <v>-36.31120410081774</v>
       </c>
       <c r="F93">
-        <v>-5.468872628488413</v>
+        <v>-6.259864094073605</v>
       </c>
       <c r="G93">
-        <v>-12.39587973122615</v>
+        <v>-10.10036994045422</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.06748772998603</v>
       </c>
       <c r="E94">
-        <v>-37.8966613429322</v>
+        <v>-38.11322429116402</v>
       </c>
       <c r="F94">
-        <v>-5.487113278698058</v>
+        <v>-6.375948602616018</v>
       </c>
       <c r="G94">
-        <v>-12.0050042129573</v>
+        <v>-10.82684879982308</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.40566532453642</v>
       </c>
       <c r="E95">
-        <v>-39.46159327660689</v>
+        <v>-40.90154159190688</v>
       </c>
       <c r="F95">
-        <v>-5.644195760923526</v>
+        <v>-6.818587966853038</v>
       </c>
       <c r="G95">
-        <v>-12.30134773809855</v>
+        <v>-11.81224557122616</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.80326193607198</v>
       </c>
       <c r="E96">
-        <v>-41.3906303701573</v>
+        <v>-42.25108118788074</v>
       </c>
       <c r="F96">
-        <v>-5.794500541059287</v>
+        <v>-6.18114185468336</v>
       </c>
       <c r="G96">
-        <v>-12.100369636361</v>
+        <v>-11.6663821480226</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.25821759616663</v>
       </c>
       <c r="E97">
-        <v>-44.5412233272768</v>
+        <v>-44.71441481570015</v>
       </c>
       <c r="F97">
-        <v>-5.640780402121783</v>
+        <v>-5.813365780290644</v>
       </c>
       <c r="G97">
-        <v>-12.73174228882935</v>
+        <v>-11.19609122435051</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.7665118242481</v>
       </c>
       <c r="E98">
-        <v>-46.27943505461799</v>
+        <v>-47.48457972838327</v>
       </c>
       <c r="F98">
-        <v>-5.605682475265168</v>
+        <v>-6.114512122639181</v>
       </c>
       <c r="G98">
-        <v>-12.79337019215884</v>
+        <v>-10.54425687423746</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.30272668097807</v>
       </c>
       <c r="E99">
-        <v>-48.16607883874561</v>
+        <v>-47.20951568868337</v>
       </c>
       <c r="F99">
-        <v>-5.750494351152967</v>
+        <v>-6.525701690061515</v>
       </c>
       <c r="G99">
-        <v>-13.71304409572624</v>
+        <v>-11.42366690804892</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.89110591598417</v>
       </c>
       <c r="E100">
-        <v>-49.63832989126081</v>
+        <v>-49.55718982610988</v>
       </c>
       <c r="F100">
-        <v>-5.761350105966654</v>
+        <v>-6.117008821991219</v>
       </c>
       <c r="G100">
-        <v>-13.79094357676902</v>
+        <v>-12.59433785480604</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.46309126823914</v>
       </c>
       <c r="E101">
-        <v>-51.83518999457286</v>
+        <v>-53.05384197418453</v>
       </c>
       <c r="F101">
-        <v>-5.860879277780417</v>
+        <v>-6.173650928259844</v>
       </c>
       <c r="G101">
-        <v>-13.6557244363043</v>
+        <v>-13.34414291824099</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.10801046380216</v>
       </c>
       <c r="E102">
-        <v>-53.98760765397365</v>
+        <v>-53.50285375746707</v>
       </c>
       <c r="F102">
-        <v>-5.789185735802926</v>
+        <v>-6.162506901589982</v>
       </c>
       <c r="G102">
-        <v>-13.64612358202137</v>
+        <v>-12.62839037214996</v>
       </c>
     </row>
   </sheetData>
